--- a/files/Электричество 2025.xlsx
+++ b/files/Электричество 2025.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="209" documentId="11_414869A8D3DA370CAF078454DD5A78F7D2006379" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1ADB3C9F-79C8-475B-A492-39423F615996}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866B6194-FA86-41F4-B970-F310866883D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="285" yWindow="0" windowWidth="28800" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23040" yWindow="1092" windowWidth="21600" windowHeight="11292" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -22,8 +22,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -31,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="49">
   <si>
     <t>дата отчета</t>
   </si>
@@ -64,9 +62,6 @@
   </si>
   <si>
     <t>кВт/ день</t>
-  </si>
-  <si>
-    <t>по 31.10.24</t>
   </si>
   <si>
     <t>2025 год</t>
@@ -690,7 +685,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -789,15 +784,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1085,7 +1077,7 @@
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
     <col min="2" max="2" width="9.85546875" style="14" customWidth="1"/>
     <col min="3" max="3" width="11.5703125" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" style="15" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.7109375" style="16" customWidth="1"/>
     <col min="6" max="6" width="11" style="10" customWidth="1"/>
     <col min="7" max="7" width="8.85546875" style="10"/>
@@ -1093,7 +1085,7 @@
     <col min="9" max="9" width="14" style="15" customWidth="1"/>
     <col min="10" max="10" width="10" style="10" customWidth="1"/>
     <col min="11" max="11" width="8.85546875" style="10"/>
-    <col min="12" max="12" width="12.5703125" style="10" customWidth="1"/>
+    <col min="12" max="12" width="17.140625" style="10" customWidth="1"/>
     <col min="13" max="16384" width="8.85546875" style="10"/>
   </cols>
   <sheetData>
@@ -1126,10 +1118,10 @@
         <v>6</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K1" s="31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L1" s="30" t="s">
         <v>5</v>
@@ -2565,7 +2557,7 @@
         <v>85496.722999999925</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="11">
         <v>45629</v>
       </c>
@@ -2588,7 +2580,7 @@
         <v>85917.532999999923</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="11">
         <v>45630</v>
       </c>
@@ -2611,7 +2603,7 @@
         <v>87913.682999999917</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="11">
         <v>45631</v>
       </c>
@@ -2634,7 +2626,7 @@
         <v>92013.882999999914</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="11">
         <v>45632</v>
       </c>
@@ -2657,7 +2649,7 @@
         <v>94279.782999999908</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="11">
         <v>45635</v>
       </c>
@@ -2680,7 +2672,7 @@
         <v>97646.262999999904</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="11"/>
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
@@ -2698,11 +2690,8 @@
       <c r="J70" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="L70" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="11">
         <v>45636</v>
       </c>
@@ -2731,7 +2720,7 @@
         <v>46602.01299999989</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="11">
         <v>45637</v>
       </c>
@@ -2754,7 +2743,7 @@
         <v>49817.432999999888</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="11">
         <v>45638</v>
       </c>
@@ -2777,7 +2766,7 @@
         <v>51964.642999999887</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="11">
         <v>45639</v>
       </c>
@@ -2800,7 +2789,7 @@
         <v>53701.83299999989</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="11">
         <v>45642</v>
       </c>
@@ -2823,7 +2812,7 @@
         <v>58870.242999999886</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="11">
         <v>45643</v>
       </c>
@@ -2846,7 +2835,7 @@
         <v>60326.892999999887</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="11">
         <v>45644</v>
       </c>
@@ -2869,7 +2858,7 @@
         <v>63661.002999999888</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="11">
         <v>45645</v>
       </c>
@@ -2892,7 +2881,7 @@
         <v>65430.562999999886</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="11">
         <v>45646</v>
       </c>
@@ -2915,7 +2904,7 @@
         <v>67556.192999999883</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="11">
         <v>45649</v>
       </c>
@@ -3032,7 +3021,7 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="70" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B85" s="74"/>
       <c r="C85" s="72"/>
@@ -3442,7 +3431,7 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="73" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B103" s="74"/>
       <c r="C103" s="72"/>
@@ -3921,7 +3910,7 @@
     </row>
     <row r="124" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="66" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B124" s="67"/>
       <c r="C124" s="68"/>
@@ -4131,7 +4120,7 @@
         <v>205144.53299999991</v>
       </c>
       <c r="J132" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -4205,7 +4194,7 @@
         <v>147758.44299999988</v>
       </c>
       <c r="J135" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -4231,7 +4220,7 @@
         <v>151739.95299999989</v>
       </c>
       <c r="K136" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L136" s="48">
         <v>28232.58</v>
@@ -4260,7 +4249,7 @@
         <v>157868.67299999989</v>
       </c>
       <c r="K137" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L137" s="49">
         <v>29405.49</v>
@@ -4289,7 +4278,7 @@
         <v>162055.19299999988</v>
       </c>
       <c r="K138" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L138" s="50">
         <v>23620.6</v>
@@ -4320,8 +4309,8 @@
       <c r="K139" s="52">
         <v>45770</v>
       </c>
-      <c r="L139" s="51">
-        <v>-81258.67</v>
+      <c r="L139" s="48">
+        <v>22474.243333333299</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -4347,11 +4336,13 @@
         <v>176654.06299999988</v>
       </c>
       <c r="K140" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="L140" s="51"/>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="L140" s="49">
+        <v>20168.253333333301</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="24">
         <v>45741</v>
       </c>
@@ -4373,7 +4364,9 @@
         <f t="shared" si="3"/>
         <v>180495.30299999987</v>
       </c>
-      <c r="L141" s="51"/>
+      <c r="L141" s="50">
+        <v>17862.2633333333</v>
+      </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="24">
@@ -4397,7 +4390,9 @@
         <f t="shared" si="3"/>
         <v>184973.15299999987</v>
       </c>
-      <c r="L142" s="51"/>
+      <c r="L142" s="48">
+        <v>15556.2733333333</v>
+      </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="24">
@@ -4421,9 +4416,11 @@
         <f t="shared" si="3"/>
         <v>187800.13299999989</v>
       </c>
-      <c r="L143" s="51"/>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L143" s="49">
+        <v>13250.2833333333</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="24">
         <v>45744</v>
       </c>
@@ -4445,7 +4442,9 @@
         <f t="shared" si="3"/>
         <v>190605.53299999988</v>
       </c>
-      <c r="L144" s="51"/>
+      <c r="L144" s="50">
+        <v>10944.2933333333</v>
+      </c>
     </row>
     <row r="145" spans="1:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="37">
@@ -4469,11 +4468,13 @@
         <f>I144+D145-H145</f>
         <v>198838.30299999987</v>
       </c>
-      <c r="L145" s="51"/>
+      <c r="L145" s="48">
+        <v>8638.3033333333406</v>
+      </c>
     </row>
     <row r="146" spans="1:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="59" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B146" s="60"/>
       <c r="C146" s="61"/>
@@ -4490,7 +4491,10 @@
         <v>198838.30299999987</v>
       </c>
       <c r="J146" s="79"/>
-      <c r="L146" s="51"/>
+      <c r="L146" s="54">
+        <f>J158*K158</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147" s="32"/>
@@ -4505,7 +4509,7 @@
         <v>45769</v>
       </c>
       <c r="G147" s="44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H147" s="57">
         <v>100000</v>
@@ -4514,7 +4518,10 @@
         <f t="shared" si="3"/>
         <v>98838.302999999869</v>
       </c>
-      <c r="L147" s="51"/>
+      <c r="L147" s="54">
+        <f>J159*K159</f>
+        <v>788.79449999999997</v>
+      </c>
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148" s="32"/>
@@ -4529,7 +4536,7 @@
         <v>45770</v>
       </c>
       <c r="G148" s="44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H148" s="54">
         <v>318741.33</v>
@@ -4538,7 +4545,10 @@
         <f t="shared" si="3"/>
         <v>-219903.02700000015</v>
       </c>
-      <c r="L148" s="51"/>
+      <c r="L148" s="54">
+        <f>J160*K160</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149" s="32"/>
@@ -4550,7 +4560,7 @@
       </c>
       <c r="E149" s="9"/>
       <c r="F149" s="46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G149" s="6"/>
       <c r="H149" s="54">
@@ -4560,7 +4570,10 @@
         <f t="shared" si="3"/>
         <v>-162870.02700000015</v>
       </c>
-      <c r="L149" s="51"/>
+      <c r="L149" s="54">
+        <f>J161*K161</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150" s="32"/>
@@ -4572,7 +4585,7 @@
       </c>
       <c r="E150" s="9"/>
       <c r="F150" s="46" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G150" s="6"/>
       <c r="H150" s="54">
@@ -4582,11 +4595,14 @@
         <f t="shared" si="3"/>
         <v>-161790.02700000015</v>
       </c>
-      <c r="L150" s="51"/>
+      <c r="L150" s="54">
+        <f t="shared" ref="L150:L155" si="4">J162*K162</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B151" s="7">
         <v>1576</v>
@@ -4606,7 +4622,10 @@
         <f t="shared" si="3"/>
         <v>-144784.98700000014</v>
       </c>
-      <c r="L151" s="51"/>
+      <c r="L151" s="54">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152" s="11">
@@ -4630,9 +4649,12 @@
         <f t="shared" si="3"/>
         <v>-141655.88700000013</v>
       </c>
-      <c r="L152" s="51"/>
-    </row>
-    <row r="153" spans="1:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L152" s="54">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153" s="11">
         <v>45777</v>
       </c>
@@ -4654,13 +4676,16 @@
         <f t="shared" si="3"/>
         <v>-137534.10700000013</v>
       </c>
-      <c r="L153" s="51"/>
+      <c r="L153" s="54">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="154" spans="1:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="65"/>
-      <c r="B154" s="84"/>
-      <c r="C154" s="85"/>
-      <c r="D154" s="86">
+      <c r="B154" s="83"/>
+      <c r="C154" s="84"/>
+      <c r="D154" s="85">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4675,14 +4700,14 @@
         <f>I153+D154-H154</f>
         <v>-137534.10700000013</v>
       </c>
-      <c r="L154" s="82">
-        <f ca="1">SUM(L136:L155)</f>
+      <c r="L154" s="54">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B155" s="33">
         <v>1705</v>
@@ -4699,18 +4724,18 @@
       <c r="G155" s="44"/>
       <c r="H155" s="57"/>
       <c r="I155" s="81">
-        <f t="shared" ref="I155:I178" si="4">I154+D155-H155</f>
+        <f t="shared" ref="I155:I177" si="5">I154+D155-H155</f>
         <v>-119137.15700000014</v>
       </c>
-      <c r="J155" s="83">
+      <c r="J155" s="82">
         <v>16.833600000000001</v>
       </c>
       <c r="K155" s="6">
         <v>7.5</v>
       </c>
       <c r="L155" s="54">
-        <f>J155*K155</f>
-        <v>126.25200000000001</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="M155" s="6"/>
       <c r="N155" s="6"/>
@@ -4718,7 +4743,7 @@
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B156" s="7">
         <v>108</v>
@@ -4727,7 +4752,7 @@
         <v>10.79</v>
       </c>
       <c r="D156" s="34">
-        <f t="shared" ref="D156:D177" si="5">B156*C156</f>
+        <f t="shared" ref="D156:D176" si="6">B156*C156</f>
         <v>1165.32</v>
       </c>
       <c r="E156" s="9"/>
@@ -4735,13 +4760,13 @@
       <c r="G156" s="6"/>
       <c r="H156" s="54"/>
       <c r="I156" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-117971.83700000013</v>
       </c>
       <c r="J156" s="6"/>
       <c r="K156" s="6"/>
       <c r="L156" s="54">
-        <f t="shared" ref="L156:L162" si="6">J156*K156</f>
+        <f t="shared" ref="L156:L162" si="7">J156*K156</f>
         <v>0</v>
       </c>
       <c r="M156" s="6"/>
@@ -4750,7 +4775,7 @@
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B157" s="7">
         <v>364</v>
@@ -4767,13 +4792,13 @@
       <c r="G157" s="6"/>
       <c r="H157" s="54"/>
       <c r="I157" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-114044.27700000013</v>
       </c>
       <c r="J157" s="6"/>
       <c r="K157" s="6"/>
       <c r="L157" s="54">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M157" s="6"/>
@@ -4782,7 +4807,7 @@
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B158" s="7">
         <v>364</v>
@@ -4799,22 +4824,18 @@
       <c r="G158" s="6"/>
       <c r="H158" s="54"/>
       <c r="I158" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-110116.71700000014</v>
       </c>
       <c r="J158" s="6"/>
       <c r="K158" s="6"/>
-      <c r="L158" s="54">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
       <c r="M158" s="6"/>
       <c r="N158" s="6"/>
       <c r="O158" s="6"/>
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A159" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B159" s="7">
         <v>730</v>
@@ -4823,7 +4844,7 @@
         <v>10.79</v>
       </c>
       <c r="D159" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7876.7</v>
       </c>
       <c r="E159" s="9"/>
@@ -4831,7 +4852,7 @@
       <c r="G159" s="6"/>
       <c r="H159" s="54"/>
       <c r="I159" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-102240.01700000014</v>
       </c>
       <c r="J159" s="6">
@@ -4839,10 +4860,6 @@
       </c>
       <c r="K159" s="6">
         <v>7.5</v>
-      </c>
-      <c r="L159" s="54">
-        <f t="shared" si="6"/>
-        <v>788.79449999999997</v>
       </c>
       <c r="M159" s="6"/>
       <c r="N159" s="6"/>
@@ -4850,7 +4867,7 @@
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B160" s="7">
         <v>539</v>
@@ -4859,7 +4876,7 @@
         <v>10.79</v>
       </c>
       <c r="D160" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5815.8099999999995</v>
       </c>
       <c r="E160" s="9"/>
@@ -4867,22 +4884,18 @@
       <c r="G160" s="6"/>
       <c r="H160" s="54"/>
       <c r="I160" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-96424.20700000014</v>
       </c>
       <c r="J160" s="6"/>
       <c r="K160" s="6"/>
-      <c r="L160" s="54">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
       <c r="M160" s="6"/>
       <c r="N160" s="6"/>
       <c r="O160" s="6"/>
     </row>
     <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B161" s="7">
         <v>261</v>
@@ -4891,7 +4904,7 @@
         <v>10.79</v>
       </c>
       <c r="D161" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2816.1899999999996</v>
       </c>
       <c r="E161" s="9"/>
@@ -4899,22 +4912,18 @@
       <c r="G161" s="6"/>
       <c r="H161" s="54"/>
       <c r="I161" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-93608.017000000138</v>
       </c>
       <c r="J161" s="6"/>
       <c r="K161" s="6"/>
-      <c r="L161" s="54">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
       <c r="M161" s="6"/>
       <c r="N161" s="6"/>
       <c r="O161" s="6"/>
     </row>
     <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162" s="44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B162" s="33">
         <v>390</v>
@@ -4923,7 +4932,7 @@
         <v>10.79</v>
       </c>
       <c r="D162" s="34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4208.0999999999995</v>
       </c>
       <c r="E162" s="43"/>
@@ -4931,13 +4940,13 @@
       <c r="G162" s="44"/>
       <c r="H162" s="57"/>
       <c r="I162" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-89399.917000000132</v>
       </c>
       <c r="J162" s="6"/>
       <c r="K162" s="6"/>
       <c r="L162" s="54">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M162" s="6"/>
@@ -4946,7 +4955,7 @@
     </row>
     <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B163" s="7">
         <v>308</v>
@@ -4955,7 +4964,7 @@
         <v>10.79</v>
       </c>
       <c r="D163" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3323.3199999999997</v>
       </c>
       <c r="E163" s="9"/>
@@ -4963,7 +4972,7 @@
       <c r="G163" s="6"/>
       <c r="H163" s="54"/>
       <c r="I163" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-86076.597000000125</v>
       </c>
       <c r="J163" s="6"/>
@@ -4977,7 +4986,7 @@
     </row>
     <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164" s="44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B164" s="33">
         <v>390</v>
@@ -4986,7 +4995,7 @@
         <v>10.79</v>
       </c>
       <c r="D164" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4208.0999999999995</v>
       </c>
       <c r="E164" s="43"/>
@@ -4994,7 +5003,7 @@
       <c r="G164" s="44"/>
       <c r="H164" s="57"/>
       <c r="I164" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-81868.497000000119</v>
       </c>
       <c r="J164" s="6"/>
@@ -5006,14 +5015,14 @@
     </row>
     <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165" s="44" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B165" s="7"/>
       <c r="C165" s="8">
         <v>10.79</v>
       </c>
       <c r="D165" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E165" s="9"/>
@@ -5021,7 +5030,7 @@
       <c r="G165" s="6"/>
       <c r="H165" s="54"/>
       <c r="I165" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-81868.497000000119</v>
       </c>
       <c r="J165" s="6"/>
@@ -5033,14 +5042,14 @@
     </row>
     <row r="166" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A166" s="44" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B166" s="7"/>
       <c r="C166" s="8">
         <v>10.79</v>
       </c>
       <c r="D166" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E166" s="9"/>
@@ -5048,7 +5057,7 @@
       <c r="G166" s="6"/>
       <c r="H166" s="54"/>
       <c r="I166" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-81868.497000000119</v>
       </c>
       <c r="J166" s="6"/>
@@ -5060,14 +5069,14 @@
     </row>
     <row r="167" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167" s="44" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B167" s="7"/>
       <c r="C167" s="8">
         <v>10.79</v>
       </c>
       <c r="D167" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E167" s="9"/>
@@ -5075,7 +5084,7 @@
       <c r="G167" s="6"/>
       <c r="H167" s="54"/>
       <c r="I167" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-81868.497000000119</v>
       </c>
       <c r="J167" s="6"/>
@@ -5087,7 +5096,7 @@
     </row>
     <row r="168" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A168" s="44" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B168" s="7">
         <v>1172</v>
@@ -5096,19 +5105,19 @@
         <v>10.79</v>
       </c>
       <c r="D168" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12645.88</v>
       </c>
       <c r="E168" s="9"/>
       <c r="F168" s="6"/>
       <c r="G168" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H168" s="54">
         <v>112331.84</v>
       </c>
       <c r="I168" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-181554.45700000011</v>
       </c>
       <c r="J168" s="6"/>
@@ -5120,7 +5129,7 @@
     </row>
     <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169" s="44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B169" s="7">
         <v>329</v>
@@ -5129,7 +5138,7 @@
         <v>10.79</v>
       </c>
       <c r="D169" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3549.91</v>
       </c>
       <c r="E169" s="9"/>
@@ -5149,7 +5158,7 @@
     </row>
     <row r="170" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170" s="44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B170" s="7">
         <v>85</v>
@@ -5158,7 +5167,7 @@
         <v>10.79</v>
       </c>
       <c r="D170" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>917.15</v>
       </c>
       <c r="E170" s="9"/>
@@ -5166,7 +5175,7 @@
       <c r="G170" s="6"/>
       <c r="H170" s="54"/>
       <c r="I170" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-177087.39700000011</v>
       </c>
       <c r="J170" s="6"/>
@@ -5178,7 +5187,7 @@
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171" s="44" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B171" s="7">
         <v>192</v>
@@ -5187,7 +5196,7 @@
         <v>10.79</v>
       </c>
       <c r="D171" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2071.6799999999998</v>
       </c>
       <c r="E171" s="9"/>
@@ -5195,7 +5204,7 @@
       <c r="G171" s="6"/>
       <c r="H171" s="54"/>
       <c r="I171" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-175015.71700000012</v>
       </c>
       <c r="J171" s="6"/>
@@ -5207,7 +5216,7 @@
     </row>
     <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172" s="44" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B172" s="7">
         <v>227</v>
@@ -5216,7 +5225,7 @@
         <v>10.79</v>
       </c>
       <c r="D172" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2449.33</v>
       </c>
       <c r="E172" s="9"/>
@@ -5224,7 +5233,7 @@
       <c r="G172" s="6"/>
       <c r="H172" s="54"/>
       <c r="I172" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-172566.38700000013</v>
       </c>
       <c r="J172" s="6"/>
@@ -5236,7 +5245,7 @@
     </row>
     <row r="173" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A173" s="44" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B173" s="7">
         <v>119</v>
@@ -5245,7 +5254,7 @@
         <v>10.79</v>
       </c>
       <c r="D173" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1284.01</v>
       </c>
       <c r="E173" s="9"/>
@@ -5253,7 +5262,7 @@
       <c r="G173" s="6"/>
       <c r="H173" s="54"/>
       <c r="I173" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-171282.37700000012</v>
       </c>
       <c r="J173" s="6"/>
@@ -5265,14 +5274,14 @@
     </row>
     <row r="174" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A174" s="44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B174" s="7"/>
       <c r="C174" s="8">
         <v>10.79</v>
       </c>
       <c r="D174" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E174" s="9"/>
@@ -5280,7 +5289,7 @@
       <c r="G174" s="6"/>
       <c r="H174" s="54"/>
       <c r="I174" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-171282.37700000012</v>
       </c>
       <c r="J174" s="6"/>
@@ -5292,14 +5301,14 @@
     </row>
     <row r="175" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A175" s="44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B175" s="7"/>
       <c r="C175" s="8">
         <v>10.79</v>
       </c>
       <c r="D175" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E175" s="9"/>
@@ -5307,7 +5316,7 @@
       <c r="G175" s="6"/>
       <c r="H175" s="54"/>
       <c r="I175" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-171282.37700000012</v>
       </c>
       <c r="J175" s="6"/>
@@ -5319,14 +5328,14 @@
     </row>
     <row r="176" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A176" s="44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B176" s="7"/>
       <c r="C176" s="8">
         <v>10.79</v>
       </c>
       <c r="D176" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E176" s="9"/>
@@ -5334,7 +5343,7 @@
       <c r="G176" s="6"/>
       <c r="H176" s="54"/>
       <c r="I176" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-171282.37700000012</v>
       </c>
       <c r="J176" s="6"/>
@@ -5346,7 +5355,7 @@
     </row>
     <row r="177" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A177" s="44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B177" s="7">
         <v>344</v>
@@ -5355,7 +5364,7 @@
         <v>10.79</v>
       </c>
       <c r="D177" s="8">
-        <f t="shared" si="5"/>
+        <f>B177*C177</f>
         <v>3711.7599999999998</v>
       </c>
       <c r="E177" s="9"/>
@@ -5363,7 +5372,7 @@
       <c r="G177" s="6"/>
       <c r="H177" s="54"/>
       <c r="I177" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-167570.61700000011</v>
       </c>
       <c r="J177" s="6"/>
@@ -5374,19 +5383,26 @@
       <c r="O177" s="6"/>
     </row>
     <row r="178" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A178" s="89" t="s">
-        <v>24</v>
-      </c>
-      <c r="B178" s="87"/>
-      <c r="C178" s="88"/>
-      <c r="D178" s="88"/>
+      <c r="A178" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="B178" s="7">
+        <v>344</v>
+      </c>
+      <c r="C178" s="8">
+        <v>10.79</v>
+      </c>
+      <c r="D178" s="8">
+        <f>B178*C178</f>
+        <v>3711.7599999999998</v>
+      </c>
       <c r="E178" s="9"/>
       <c r="F178" s="6"/>
       <c r="G178" s="6"/>
       <c r="H178" s="54"/>
       <c r="I178" s="8">
-        <f t="shared" si="4"/>
-        <v>-167570.61700000011</v>
+        <f>I177+D178-H178</f>
+        <v>-163858.85700000011</v>
       </c>
       <c r="J178" s="6"/>
       <c r="K178" s="6"/>
@@ -5397,12 +5413,12 @@
     </row>
     <row r="179" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D179" s="15">
-        <f>SUM(D155:D177)</f>
-        <v>82295.329999999973</v>
+        <f>SUM(D2:D178)</f>
+        <v>516313.473</v>
       </c>
       <c r="L179" s="51">
-        <f>SUM(L155:L178)</f>
-        <v>915.04649999999992</v>
+        <f>SUM(L2:L178)</f>
+        <v>190941.37783333313</v>
       </c>
     </row>
   </sheetData>
